--- a/데이터/opened_course2024_1.xlsx
+++ b/데이터/opened_course2024_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\AI융개_팀플\데이터\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77147AD7-377D-4239-99E2-04A3168CB5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DFEF7A-E38B-4AE4-BB17-946779A41E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="심화전공2024_1" sheetId="4" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2020" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2020" uniqueCount="409">
   <si>
     <t>수리통계데이터사이언스학부</t>
   </si>
@@ -1256,6 +1256,10 @@
   </si>
   <si>
     <t>서비스디자인공학과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바이오식품공학과</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1645,6 +1649,7 @@
   <cols>
     <col min="1" max="1" width="21.3828125" customWidth="1"/>
     <col min="2" max="2" width="27.07421875" customWidth="1"/>
+    <col min="3" max="3" width="18.15234375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -2601,7 +2606,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>211</v>
+        <v>408</v>
       </c>
       <c r="B57" t="s">
         <v>362</v>
@@ -3103,7 +3108,8 @@
   <dimension ref="A1:E184"/>
   <sheetFormatPr defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="17.61328125" customWidth="1"/>
+    <col min="1" max="1" width="27.15234375" customWidth="1"/>
+    <col min="2" max="2" width="31.3828125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">

--- a/데이터/opened_course2024_1.xlsx
+++ b/데이터/opened_course2024_1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\AI융개_팀플\데이터\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DFEF7A-E38B-4AE4-BB17-946779A41E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14754E27-28FE-4DDA-A571-6EC1643D18DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="심화전공2024_1" sheetId="4" r:id="rId1"/>
@@ -627,9 +627,6 @@
     <t>UX 프로토타이핑</t>
   </si>
   <si>
-    <t>지능형IoT</t>
-  </si>
-  <si>
     <t>IoT창의공학설계</t>
   </si>
   <si>
@@ -1260,6 +1257,10 @@
   </si>
   <si>
     <t>바이오식품공학과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지능형IoT</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1674,13 +1675,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -1691,13 +1692,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -1705,16 +1706,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1722,16 +1723,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B5" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -1739,16 +1740,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -1756,16 +1757,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -1773,16 +1774,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B8" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -1790,16 +1791,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -1807,16 +1808,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -1824,16 +1825,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D11" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -1841,16 +1842,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B12" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -1858,16 +1859,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B13" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C13" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -1875,16 +1876,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C14" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D14" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -1892,16 +1893,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B15" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C15" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D15" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -1909,16 +1910,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B16" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C16" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D16" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -1926,16 +1927,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B17" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C17" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D17" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -1943,16 +1944,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B18" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C18" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D18" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -1960,16 +1961,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B19" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C19" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D19" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -1977,16 +1978,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C20" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D20" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E20">
         <v>3</v>
@@ -1994,16 +1995,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C21" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D21" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -2011,16 +2012,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C22" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D22" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E22">
         <v>3</v>
@@ -2028,16 +2029,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C23" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D23" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E23">
         <v>3</v>
@@ -2045,16 +2046,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C24" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D24" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E24">
         <v>3</v>
@@ -2062,16 +2063,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B25" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C25" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D25" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E25">
         <v>3</v>
@@ -2079,16 +2080,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B26" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C26" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D26" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E26">
         <v>3</v>
@@ -2096,16 +2097,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B27" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C27" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D27" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E27">
         <v>3</v>
@@ -2113,16 +2114,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B28" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C28" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D28" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E28">
         <v>3</v>
@@ -2130,16 +2131,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B29" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C29" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D29" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E29">
         <v>3</v>
@@ -2147,16 +2148,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B30" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C30" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D30" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E30">
         <v>3</v>
@@ -2164,16 +2165,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B31" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C31" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D31" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E31">
         <v>3</v>
@@ -2181,16 +2182,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B32" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C32" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D32" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E32">
         <v>3</v>
@@ -2198,16 +2199,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B33" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C33" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D33" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E33">
         <v>3</v>
@@ -2215,16 +2216,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B34" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C34" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D34" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E34">
         <v>3</v>
@@ -2232,16 +2233,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B35" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C35" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D35" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E35">
         <v>3</v>
@@ -2249,16 +2250,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B36" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C36" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D36" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E36">
         <v>3</v>
@@ -2266,16 +2267,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B37" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C37" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E37">
         <v>3</v>
@@ -2283,16 +2284,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B38" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C38" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D38" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E38">
         <v>3</v>
@@ -2300,16 +2301,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B39" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C39" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D39" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E39">
         <v>3</v>
@@ -2317,16 +2318,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B40" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C40" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D40" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E40">
         <v>3</v>
@@ -2334,16 +2335,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B41" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C41" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D41" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E41">
         <v>3</v>
@@ -2351,16 +2352,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B42" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C42" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D42" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E42">
         <v>3</v>
@@ -2368,16 +2369,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B43" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C43" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D43" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E43">
         <v>2</v>
@@ -2385,16 +2386,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B44" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C44" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D44" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E44">
         <v>3</v>
@@ -2402,16 +2403,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B45" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C45" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D45" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E45">
         <v>3</v>
@@ -2419,16 +2420,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B46" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C46" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D46" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -2436,16 +2437,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B47" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C47" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D47" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E47">
         <v>3</v>
@@ -2453,16 +2454,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B48" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C48" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D48" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E48">
         <v>3</v>
@@ -2470,16 +2471,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B49" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C49" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D49" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E49">
         <v>3</v>
@@ -2487,16 +2488,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B50" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C50" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D50" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E50">
         <v>3</v>
@@ -2504,16 +2505,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B51" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C51" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D51" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E51">
         <v>2</v>
@@ -2521,16 +2522,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B52" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C52" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D52" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -2538,16 +2539,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B53" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C53" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D53" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -2555,16 +2556,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B54" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C54" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D54" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -2572,16 +2573,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B55" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C55" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D55" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E55">
         <v>3</v>
@@ -2589,16 +2590,16 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B56" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C56" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D56" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E56">
         <v>2</v>
@@ -2606,16 +2607,16 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B57" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C57" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D57" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E57">
         <v>3</v>
@@ -2623,16 +2624,16 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B58" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C58" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D58" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E58">
         <v>3</v>
@@ -2640,16 +2641,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B59" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C59" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D59" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -2657,16 +2658,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B60" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C60" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D60" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E60">
         <v>2</v>
@@ -2674,16 +2675,16 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B61" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C61" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D61" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E61">
         <v>3</v>
@@ -2691,16 +2692,16 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B62" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C62" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D62" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -2711,13 +2712,13 @@
         <v>192</v>
       </c>
       <c r="B63" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C63" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D63" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E63">
         <v>3</v>
@@ -2728,13 +2729,13 @@
         <v>192</v>
       </c>
       <c r="B64" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C64" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D64" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E64">
         <v>3</v>
@@ -2745,13 +2746,13 @@
         <v>192</v>
       </c>
       <c r="B65" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C65" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D65" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E65">
         <v>3</v>
@@ -2762,13 +2763,13 @@
         <v>192</v>
       </c>
       <c r="B66" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C66" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D66" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E66">
         <v>3</v>
@@ -2779,13 +2780,13 @@
         <v>192</v>
       </c>
       <c r="B67" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C67" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E67">
         <v>3</v>
@@ -2796,13 +2797,13 @@
         <v>192</v>
       </c>
       <c r="B68" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C68" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D68" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E68">
         <v>3</v>
@@ -2813,13 +2814,13 @@
         <v>192</v>
       </c>
       <c r="B69" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C69" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D69" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E69">
         <v>2</v>
@@ -2830,13 +2831,13 @@
         <v>192</v>
       </c>
       <c r="B70" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C70" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D70" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E70">
         <v>3</v>
@@ -2847,13 +2848,13 @@
         <v>192</v>
       </c>
       <c r="B71" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C71" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D71" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E71">
         <v>3</v>
@@ -2864,13 +2865,13 @@
         <v>192</v>
       </c>
       <c r="B72" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C72" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E72">
         <v>3</v>
@@ -2878,16 +2879,16 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B73" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C73" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D73" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E73">
         <v>3</v>
@@ -2895,16 +2896,16 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B74" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C74" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D74" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E74">
         <v>3</v>
@@ -2912,16 +2913,16 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B75" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C75" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D75" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E75">
         <v>3</v>
@@ -2929,16 +2930,16 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B76" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C76" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E76">
         <v>3</v>
@@ -2946,16 +2947,16 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B77" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C77" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D77" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E77">
         <v>3</v>
@@ -2963,16 +2964,16 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B78" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C78" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D78" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E78">
         <v>3</v>
@@ -2980,16 +2981,16 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B79" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C79" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E79">
         <v>3</v>
@@ -2997,16 +2998,16 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B80" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C80" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D80" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E80">
         <v>3</v>
@@ -3014,16 +3015,16 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B81" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C81" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D81" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E81">
         <v>3</v>
@@ -3031,16 +3032,16 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B82" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C82" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D82" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E82">
         <v>3</v>
@@ -3048,16 +3049,16 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>198</v>
+        <v>408</v>
       </c>
       <c r="B83" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C83" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D83" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E83">
         <v>3</v>
@@ -3065,16 +3066,16 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>198</v>
+        <v>408</v>
       </c>
       <c r="B84" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C84" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D84" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E84">
         <v>3</v>
@@ -3082,16 +3083,16 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>198</v>
+        <v>408</v>
       </c>
       <c r="B85" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C85" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D85" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E85">
         <v>3</v>
@@ -3131,16 +3132,16 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C2" t="s">
         <v>196</v>
       </c>
       <c r="D2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -3148,16 +3149,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C3" t="s">
         <v>196</v>
       </c>
       <c r="D3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -3165,16 +3166,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C4" t="s">
         <v>196</v>
       </c>
       <c r="D4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -3182,16 +3183,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C5" t="s">
         <v>196</v>
       </c>
       <c r="D5" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -3199,16 +3200,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C6" t="s">
         <v>196</v>
       </c>
       <c r="D6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -3216,16 +3217,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C7" t="s">
         <v>196</v>
       </c>
       <c r="D7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -3233,16 +3234,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
+        <v>329</v>
+      </c>
+      <c r="B8" t="s">
         <v>330</v>
       </c>
-      <c r="B8" t="s">
-        <v>331</v>
-      </c>
       <c r="C8" t="s">
         <v>196</v>
       </c>
       <c r="D8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -3250,16 +3251,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C9" t="s">
         <v>196</v>
       </c>
       <c r="D9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -3267,16 +3268,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C10" t="s">
         <v>196</v>
       </c>
       <c r="D10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -3284,16 +3285,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B11" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C11" t="s">
         <v>196</v>
       </c>
       <c r="D11" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -3301,16 +3302,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C12" t="s">
         <v>196</v>
       </c>
       <c r="D12" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -3318,16 +3319,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B13" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C13" t="s">
         <v>196</v>
       </c>
       <c r="D13" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -3335,16 +3336,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B14" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C14" t="s">
         <v>196</v>
       </c>
       <c r="D14" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -3352,16 +3353,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B15" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C15" t="s">
         <v>196</v>
       </c>
       <c r="D15" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -3369,16 +3370,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B16" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C16" t="s">
         <v>196</v>
       </c>
       <c r="D16" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -3386,16 +3387,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
+        <v>319</v>
+      </c>
+      <c r="B17" t="s">
         <v>320</v>
       </c>
-      <c r="B17" t="s">
-        <v>321</v>
-      </c>
       <c r="C17" t="s">
         <v>196</v>
       </c>
       <c r="D17" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -3403,16 +3404,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B18" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C18" t="s">
         <v>196</v>
       </c>
       <c r="D18" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -3420,16 +3421,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B19" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C19" t="s">
         <v>196</v>
       </c>
       <c r="D19" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -3437,16 +3438,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B20" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C20" t="s">
         <v>196</v>
       </c>
       <c r="D20" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E20">
         <v>3</v>
@@ -3454,16 +3455,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B21" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C21" t="s">
         <v>196</v>
       </c>
       <c r="D21" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -3471,16 +3472,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B22" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C22" t="s">
         <v>196</v>
       </c>
       <c r="D22" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E22">
         <v>3</v>
@@ -3488,16 +3489,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B23" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C23" t="s">
         <v>196</v>
       </c>
       <c r="D23" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E23">
         <v>3</v>
@@ -3505,16 +3506,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B24" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C24" t="s">
         <v>196</v>
       </c>
       <c r="D24" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E24">
         <v>3</v>
@@ -3522,16 +3523,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B25" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C25" t="s">
         <v>196</v>
       </c>
       <c r="D25" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E25">
         <v>3</v>
@@ -3539,16 +3540,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
+        <v>310</v>
+      </c>
+      <c r="B26" t="s">
         <v>311</v>
       </c>
-      <c r="B26" t="s">
-        <v>312</v>
-      </c>
       <c r="C26" t="s">
         <v>196</v>
       </c>
       <c r="D26" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E26">
         <v>3</v>
@@ -3556,16 +3557,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B27" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C27" t="s">
         <v>196</v>
       </c>
       <c r="D27" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E27">
         <v>3</v>
@@ -3573,16 +3574,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B28" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C28" t="s">
         <v>196</v>
       </c>
       <c r="D28" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E28">
         <v>3</v>
@@ -3590,16 +3591,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B29" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C29" t="s">
         <v>196</v>
       </c>
       <c r="D29" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E29">
         <v>3</v>
@@ -3607,16 +3608,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B30" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C30" t="s">
         <v>196</v>
       </c>
       <c r="D30" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E30">
         <v>3</v>
@@ -3624,16 +3625,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B31" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C31" t="s">
         <v>196</v>
       </c>
       <c r="D31" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E31">
         <v>3</v>
@@ -3641,16 +3642,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B32" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C32" t="s">
         <v>196</v>
       </c>
       <c r="D32" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E32">
         <v>3</v>
@@ -3658,16 +3659,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
+        <v>302</v>
+      </c>
+      <c r="B33" t="s">
         <v>303</v>
       </c>
-      <c r="B33" t="s">
-        <v>304</v>
-      </c>
       <c r="C33" t="s">
         <v>196</v>
       </c>
       <c r="D33" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E33">
         <v>3</v>
@@ -3675,16 +3676,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B34" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C34" t="s">
         <v>196</v>
       </c>
       <c r="D34" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E34">
         <v>3</v>
@@ -3692,16 +3693,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B35" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C35" t="s">
         <v>196</v>
       </c>
       <c r="D35" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E35">
         <v>3</v>
@@ -3709,16 +3710,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B36" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C36" t="s">
         <v>196</v>
       </c>
       <c r="D36" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E36">
         <v>3</v>
@@ -3726,16 +3727,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B37" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C37" t="s">
         <v>196</v>
       </c>
       <c r="D37" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E37">
         <v>3</v>
@@ -3743,16 +3744,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B38" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C38" t="s">
         <v>196</v>
       </c>
       <c r="D38" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E38">
         <v>3</v>
@@ -3760,16 +3761,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B39" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C39" t="s">
         <v>196</v>
       </c>
       <c r="D39" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E39">
         <v>3</v>
@@ -3777,16 +3778,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
+        <v>295</v>
+      </c>
+      <c r="B40" t="s">
         <v>296</v>
       </c>
-      <c r="B40" t="s">
-        <v>297</v>
-      </c>
       <c r="C40" t="s">
         <v>196</v>
       </c>
       <c r="D40" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E40">
         <v>3</v>
@@ -3794,16 +3795,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C41" t="s">
         <v>196</v>
       </c>
       <c r="D41" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E41">
         <v>3</v>
@@ -3811,16 +3812,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B42" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C42" t="s">
         <v>196</v>
       </c>
       <c r="D42" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E42">
         <v>3</v>
@@ -3828,16 +3829,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B43" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C43" t="s">
         <v>196</v>
       </c>
       <c r="D43" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E43">
         <v>3</v>
@@ -3845,16 +3846,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B44" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C44" t="s">
         <v>196</v>
       </c>
       <c r="D44" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E44">
         <v>3</v>
@@ -3862,16 +3863,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B45" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C45" t="s">
         <v>196</v>
       </c>
       <c r="D45" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E45">
         <v>3</v>
@@ -3879,16 +3880,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B46" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C46" t="s">
         <v>196</v>
       </c>
       <c r="D46" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E46">
         <v>3</v>
@@ -3896,16 +3897,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B47" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C47" t="s">
         <v>196</v>
       </c>
       <c r="D47" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E47">
         <v>3</v>
@@ -3913,16 +3914,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B48" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C48" t="s">
         <v>196</v>
       </c>
       <c r="D48" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E48">
         <v>3</v>
@@ -3930,16 +3931,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B49" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C49" t="s">
         <v>196</v>
       </c>
       <c r="D49" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E49">
         <v>3</v>
@@ -3947,16 +3948,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B50" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C50" t="s">
         <v>196</v>
       </c>
       <c r="D50" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E50">
         <v>3</v>
@@ -3964,16 +3965,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B51" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C51" t="s">
         <v>196</v>
       </c>
       <c r="D51" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E51">
         <v>3</v>
@@ -3981,16 +3982,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
+        <v>287</v>
+      </c>
+      <c r="B52" t="s">
         <v>288</v>
       </c>
-      <c r="B52" t="s">
-        <v>289</v>
-      </c>
       <c r="C52" t="s">
         <v>196</v>
       </c>
       <c r="D52" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3998,16 +3999,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
+        <v>287</v>
+      </c>
+      <c r="B53" t="s">
         <v>288</v>
       </c>
-      <c r="B53" t="s">
-        <v>289</v>
-      </c>
       <c r="C53" t="s">
         <v>196</v>
       </c>
       <c r="D53" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -4015,16 +4016,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B54" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C54" t="s">
         <v>196</v>
       </c>
       <c r="D54" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -4032,16 +4033,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B55" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C55" t="s">
         <v>196</v>
       </c>
       <c r="D55" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E55">
         <v>3</v>
@@ -4049,16 +4050,16 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B56" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C56" t="s">
         <v>196</v>
       </c>
       <c r="D56" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E56">
         <v>3</v>
@@ -4066,16 +4067,16 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B57" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C57" t="s">
         <v>196</v>
       </c>
       <c r="D57" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E57">
         <v>3</v>
@@ -4083,16 +4084,16 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B58" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C58" t="s">
         <v>196</v>
       </c>
       <c r="D58" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E58">
         <v>3</v>
@@ -4100,16 +4101,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C59" t="s">
         <v>196</v>
       </c>
       <c r="D59" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E59">
         <v>3</v>
@@ -4117,16 +4118,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B60" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C60" t="s">
         <v>196</v>
       </c>
       <c r="D60" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E60">
         <v>3</v>
@@ -4134,16 +4135,16 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B61" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C61" t="s">
         <v>196</v>
       </c>
       <c r="D61" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E61">
         <v>3</v>
@@ -4151,16 +4152,16 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B62" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C62" t="s">
         <v>196</v>
       </c>
       <c r="D62" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4168,16 +4169,16 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B63" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C63" t="s">
         <v>196</v>
       </c>
       <c r="D63" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E63">
         <v>3</v>
@@ -4185,16 +4186,16 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
+        <v>279</v>
+      </c>
+      <c r="B64" t="s">
         <v>280</v>
       </c>
-      <c r="B64" t="s">
-        <v>281</v>
-      </c>
       <c r="C64" t="s">
         <v>196</v>
       </c>
       <c r="D64" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E64">
         <v>3</v>
@@ -4202,16 +4203,16 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C65" t="s">
         <v>196</v>
       </c>
       <c r="D65" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E65">
         <v>3</v>
@@ -4219,16 +4220,16 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B66" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C66" t="s">
         <v>196</v>
       </c>
       <c r="D66" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E66">
         <v>3</v>
@@ -4236,16 +4237,16 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B67" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C67" t="s">
         <v>196</v>
       </c>
       <c r="D67" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E67">
         <v>3</v>
@@ -4253,16 +4254,16 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B68" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C68" t="s">
         <v>196</v>
       </c>
       <c r="D68" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E68">
         <v>3</v>
@@ -4270,16 +4271,16 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B69" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C69" t="s">
         <v>196</v>
       </c>
       <c r="D69" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E69">
         <v>3</v>
@@ -4287,16 +4288,16 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B70" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C70" t="s">
         <v>196</v>
       </c>
       <c r="D70" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E70">
         <v>3</v>
@@ -4304,16 +4305,16 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B71" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C71" t="s">
         <v>196</v>
       </c>
       <c r="D71" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E71">
         <v>3</v>
@@ -4321,16 +4322,16 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
+        <v>271</v>
+      </c>
+      <c r="B72" t="s">
         <v>272</v>
       </c>
-      <c r="B72" t="s">
-        <v>273</v>
-      </c>
       <c r="C72" t="s">
         <v>196</v>
       </c>
       <c r="D72" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E72">
         <v>3</v>
@@ -4338,16 +4339,16 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B73" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C73" t="s">
         <v>196</v>
       </c>
       <c r="D73" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E73">
         <v>3</v>
@@ -4355,16 +4356,16 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B74" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C74" t="s">
         <v>196</v>
       </c>
       <c r="D74" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E74">
         <v>3</v>
@@ -4372,16 +4373,16 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B75" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C75" t="s">
         <v>196</v>
       </c>
       <c r="D75" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E75">
         <v>3</v>
@@ -4389,16 +4390,16 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B76" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C76" t="s">
         <v>196</v>
       </c>
       <c r="D76" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E76">
         <v>3</v>
@@ -4406,16 +4407,16 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B77" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C77" t="s">
         <v>196</v>
       </c>
       <c r="D77" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E77">
         <v>3</v>
@@ -4423,16 +4424,16 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
+        <v>265</v>
+      </c>
+      <c r="B78" t="s">
         <v>266</v>
       </c>
-      <c r="B78" t="s">
-        <v>267</v>
-      </c>
       <c r="C78" t="s">
         <v>196</v>
       </c>
       <c r="D78" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E78">
         <v>3</v>
@@ -4440,16 +4441,16 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B79" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C79" t="s">
         <v>196</v>
       </c>
       <c r="D79" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E79">
         <v>3</v>
@@ -4460,13 +4461,13 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C80" t="s">
         <v>196</v>
       </c>
       <c r="D80" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E80">
         <v>3</v>
@@ -4477,13 +4478,13 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C81" t="s">
         <v>196</v>
       </c>
       <c r="D81" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E81">
         <v>3</v>
@@ -4494,13 +4495,13 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C82" t="s">
         <v>196</v>
       </c>
       <c r="D82" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E82">
         <v>3</v>
@@ -4511,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C83" t="s">
         <v>196</v>
       </c>
       <c r="D83" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E83">
         <v>3</v>
@@ -4525,16 +4526,16 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B84" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C84" t="s">
         <v>196</v>
       </c>
       <c r="D84" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E84">
         <v>3</v>
@@ -4542,16 +4543,16 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B85" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C85" t="s">
         <v>196</v>
       </c>
       <c r="D85" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E85">
         <v>3</v>
@@ -4559,16 +4560,16 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B86" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C86" t="s">
         <v>196</v>
       </c>
       <c r="D86" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E86">
         <v>3</v>
@@ -4576,16 +4577,16 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B87" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C87" t="s">
         <v>196</v>
       </c>
       <c r="D87" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E87">
         <v>3</v>
@@ -4593,16 +4594,16 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
+        <v>255</v>
+      </c>
+      <c r="B88" t="s">
         <v>256</v>
       </c>
-      <c r="B88" t="s">
-        <v>257</v>
-      </c>
       <c r="C88" t="s">
         <v>196</v>
       </c>
       <c r="D88" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E88">
         <v>3</v>
@@ -4610,16 +4611,16 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B89" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C89" t="s">
         <v>196</v>
       </c>
       <c r="D89" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E89">
         <v>3</v>
@@ -4627,16 +4628,16 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B90" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C90" t="s">
         <v>196</v>
       </c>
       <c r="D90" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E90">
         <v>3</v>
@@ -4644,16 +4645,16 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B91" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C91" t="s">
         <v>196</v>
       </c>
       <c r="D91" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E91">
         <v>3</v>
@@ -4661,16 +4662,16 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B92" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C92" t="s">
         <v>196</v>
       </c>
       <c r="D92" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E92">
         <v>3</v>
@@ -4678,16 +4679,16 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B93" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C93" t="s">
         <v>196</v>
       </c>
       <c r="D93" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E93">
         <v>3</v>
@@ -4695,16 +4696,16 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B94" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C94" t="s">
         <v>196</v>
       </c>
       <c r="D94" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E94">
         <v>3</v>
@@ -4712,16 +4713,16 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
+        <v>249</v>
+      </c>
+      <c r="B95" t="s">
         <v>250</v>
       </c>
-      <c r="B95" t="s">
-        <v>251</v>
-      </c>
       <c r="C95" t="s">
         <v>196</v>
       </c>
       <c r="D95" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E95">
         <v>3</v>
@@ -4729,16 +4730,16 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
+        <v>249</v>
+      </c>
+      <c r="B96" t="s">
         <v>250</v>
       </c>
-      <c r="B96" t="s">
-        <v>251</v>
-      </c>
       <c r="C96" t="s">
         <v>196</v>
       </c>
       <c r="D96" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E96">
         <v>3</v>
@@ -4746,16 +4747,16 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B97" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C97" t="s">
         <v>196</v>
       </c>
       <c r="D97" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E97">
         <v>3</v>
@@ -4763,16 +4764,16 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B98" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C98" t="s">
         <v>196</v>
       </c>
       <c r="D98" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E98">
         <v>3</v>
@@ -4780,16 +4781,16 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B99" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C99" t="s">
         <v>196</v>
       </c>
       <c r="D99" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E99">
         <v>3</v>
@@ -4800,13 +4801,13 @@
         <v>1</v>
       </c>
       <c r="B100" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C100" t="s">
         <v>196</v>
       </c>
       <c r="D100" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -4817,13 +4818,13 @@
         <v>1</v>
       </c>
       <c r="B101" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C101" t="s">
         <v>196</v>
       </c>
       <c r="D101" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E101">
         <v>3</v>
@@ -4834,13 +4835,13 @@
         <v>1</v>
       </c>
       <c r="B102" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C102" t="s">
         <v>196</v>
       </c>
       <c r="D102" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E102">
         <v>3</v>
@@ -4851,13 +4852,13 @@
         <v>1</v>
       </c>
       <c r="B103" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C103" t="s">
         <v>196</v>
       </c>
       <c r="D103" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E103">
         <v>3</v>
@@ -4868,13 +4869,13 @@
         <v>1</v>
       </c>
       <c r="B104" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C104" t="s">
         <v>196</v>
       </c>
       <c r="D104" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E104">
         <v>3</v>
@@ -4885,13 +4886,13 @@
         <v>1</v>
       </c>
       <c r="B105" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C105" t="s">
         <v>196</v>
       </c>
       <c r="D105" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E105">
         <v>3</v>
@@ -4902,13 +4903,13 @@
         <v>1</v>
       </c>
       <c r="B106" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C106" t="s">
         <v>196</v>
       </c>
       <c r="D106" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E106">
         <v>3</v>
@@ -4919,13 +4920,13 @@
         <v>1</v>
       </c>
       <c r="B107" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C107" t="s">
         <v>196</v>
       </c>
       <c r="D107" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E107">
         <v>3</v>
@@ -4936,13 +4937,13 @@
         <v>1</v>
       </c>
       <c r="B108" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C108" t="s">
         <v>196</v>
       </c>
       <c r="D108" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E108">
         <v>3</v>
@@ -4953,13 +4954,13 @@
         <v>1</v>
       </c>
       <c r="B109" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C109" t="s">
         <v>196</v>
       </c>
       <c r="D109" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E109">
         <v>3</v>
@@ -4970,13 +4971,13 @@
         <v>1</v>
       </c>
       <c r="B110" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C110" t="s">
         <v>196</v>
       </c>
       <c r="D110" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E110">
         <v>3</v>
@@ -4987,13 +4988,13 @@
         <v>1</v>
       </c>
       <c r="B111" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C111" t="s">
         <v>196</v>
       </c>
       <c r="D111" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E111">
         <v>3</v>
@@ -5004,13 +5005,13 @@
         <v>1</v>
       </c>
       <c r="B112" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C112" t="s">
         <v>196</v>
       </c>
       <c r="D112" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E112">
         <v>3</v>
@@ -5021,13 +5022,13 @@
         <v>1</v>
       </c>
       <c r="B113" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C113" t="s">
         <v>196</v>
       </c>
       <c r="D113" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E113">
         <v>3</v>
@@ -5038,13 +5039,13 @@
         <v>1</v>
       </c>
       <c r="B114" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C114" t="s">
         <v>196</v>
       </c>
       <c r="D114" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E114">
         <v>3</v>
@@ -5055,13 +5056,13 @@
         <v>1</v>
       </c>
       <c r="B115" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C115" t="s">
         <v>196</v>
       </c>
       <c r="D115" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E115">
         <v>3</v>
@@ -5072,13 +5073,13 @@
         <v>1</v>
       </c>
       <c r="B116" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C116" t="s">
         <v>196</v>
       </c>
       <c r="D116" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E116">
         <v>3</v>
@@ -5089,13 +5090,13 @@
         <v>1</v>
       </c>
       <c r="B117" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C117" t="s">
         <v>196</v>
       </c>
       <c r="D117" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E117">
         <v>3</v>
@@ -5106,13 +5107,13 @@
         <v>1</v>
       </c>
       <c r="B118" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C118" t="s">
         <v>196</v>
       </c>
       <c r="D118" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E118">
         <v>3</v>
@@ -5123,13 +5124,13 @@
         <v>1</v>
       </c>
       <c r="B119" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C119" t="s">
         <v>196</v>
       </c>
       <c r="D119" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E119">
         <v>3</v>
@@ -5140,13 +5141,13 @@
         <v>1</v>
       </c>
       <c r="B120" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C120" t="s">
         <v>196</v>
       </c>
       <c r="D120" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E120">
         <v>3</v>
@@ -5157,13 +5158,13 @@
         <v>1</v>
       </c>
       <c r="B121" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C121" t="s">
         <v>196</v>
       </c>
       <c r="D121" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E121">
         <v>3</v>
@@ -5174,13 +5175,13 @@
         <v>1</v>
       </c>
       <c r="B122" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C122" t="s">
         <v>196</v>
       </c>
       <c r="D122" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E122">
         <v>3</v>
@@ -5191,13 +5192,13 @@
         <v>1</v>
       </c>
       <c r="B123" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C123" t="s">
         <v>196</v>
       </c>
       <c r="D123" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E123">
         <v>3</v>
@@ -5208,13 +5209,13 @@
         <v>1</v>
       </c>
       <c r="B124" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C124" t="s">
         <v>196</v>
       </c>
       <c r="D124" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E124">
         <v>3</v>
@@ -5225,13 +5226,13 @@
         <v>1</v>
       </c>
       <c r="B125" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C125" t="s">
         <v>196</v>
       </c>
       <c r="D125" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E125">
         <v>3</v>
@@ -5242,13 +5243,13 @@
         <v>1</v>
       </c>
       <c r="B126" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C126" t="s">
         <v>196</v>
       </c>
       <c r="D126" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E126">
         <v>3</v>
@@ -5259,13 +5260,13 @@
         <v>1</v>
       </c>
       <c r="B127" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C127" t="s">
         <v>196</v>
       </c>
       <c r="D127" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E127">
         <v>3</v>
@@ -5276,13 +5277,13 @@
         <v>1</v>
       </c>
       <c r="B128" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C128" t="s">
         <v>196</v>
       </c>
       <c r="D128" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E128">
         <v>3</v>
@@ -5293,13 +5294,13 @@
         <v>1</v>
       </c>
       <c r="B129" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C129" t="s">
         <v>196</v>
       </c>
       <c r="D129" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E129">
         <v>3</v>
@@ -5310,13 +5311,13 @@
         <v>1</v>
       </c>
       <c r="B130" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C130" t="s">
         <v>196</v>
       </c>
       <c r="D130" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E130">
         <v>3</v>
@@ -5327,13 +5328,13 @@
         <v>1</v>
       </c>
       <c r="B131" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C131" t="s">
         <v>196</v>
       </c>
       <c r="D131" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E131">
         <v>3</v>
@@ -5344,13 +5345,13 @@
         <v>1</v>
       </c>
       <c r="B132" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C132" t="s">
         <v>196</v>
       </c>
       <c r="D132" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E132">
         <v>3</v>
@@ -5361,13 +5362,13 @@
         <v>1</v>
       </c>
       <c r="B133" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C133" t="s">
         <v>196</v>
       </c>
       <c r="D133" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E133">
         <v>3</v>
@@ -5375,16 +5376,16 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B134" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C134" t="s">
         <v>196</v>
       </c>
       <c r="D134" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E134">
         <v>3</v>
@@ -5392,16 +5393,16 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B135" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C135" t="s">
         <v>196</v>
       </c>
       <c r="D135" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E135">
         <v>3</v>
@@ -5409,7 +5410,7 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B136" t="s">
         <v>197</v>
@@ -5418,7 +5419,7 @@
         <v>196</v>
       </c>
       <c r="D136" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E136">
         <v>3</v>
@@ -5426,7 +5427,7 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B137" t="s">
         <v>197</v>
@@ -5435,7 +5436,7 @@
         <v>196</v>
       </c>
       <c r="D137" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E137">
         <v>3</v>
@@ -5443,16 +5444,16 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B138" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C138" t="s">
         <v>196</v>
       </c>
       <c r="D138" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E138">
         <v>3</v>
@@ -5460,16 +5461,16 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B139" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C139" t="s">
         <v>196</v>
       </c>
       <c r="D139" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E139">
         <v>3</v>
@@ -5477,16 +5478,16 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B140" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C140" t="s">
         <v>196</v>
       </c>
       <c r="D140" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E140">
         <v>3</v>
@@ -5494,16 +5495,16 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B141" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C141" t="s">
         <v>196</v>
       </c>
       <c r="D141" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E141">
         <v>3</v>
@@ -5511,16 +5512,16 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B142" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C142" t="s">
         <v>196</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E142">
         <v>3</v>
@@ -5528,16 +5529,16 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
+        <v>231</v>
+      </c>
+      <c r="B143" t="s">
         <v>232</v>
       </c>
-      <c r="B143" t="s">
-        <v>233</v>
-      </c>
       <c r="C143" t="s">
         <v>196</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E143">
         <v>3</v>
@@ -5545,16 +5546,16 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
+        <v>231</v>
+      </c>
+      <c r="B144" t="s">
         <v>232</v>
       </c>
-      <c r="B144" t="s">
-        <v>233</v>
-      </c>
       <c r="C144" t="s">
         <v>196</v>
       </c>
       <c r="D144" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E144">
         <v>3</v>
@@ -5562,16 +5563,16 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
+        <v>231</v>
+      </c>
+      <c r="B145" t="s">
         <v>232</v>
       </c>
-      <c r="B145" t="s">
-        <v>233</v>
-      </c>
       <c r="C145" t="s">
         <v>196</v>
       </c>
       <c r="D145" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E145">
         <v>3</v>
@@ -5579,16 +5580,16 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B146" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C146" t="s">
         <v>196</v>
       </c>
       <c r="D146" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E146">
         <v>3</v>
@@ -5596,16 +5597,16 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B147" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C147" t="s">
         <v>196</v>
       </c>
       <c r="D147" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E147">
         <v>3</v>
@@ -5613,16 +5614,16 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B148" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C148" t="s">
         <v>196</v>
       </c>
       <c r="D148" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E148">
         <v>2</v>
@@ -5630,16 +5631,16 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B149" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C149" t="s">
         <v>196</v>
       </c>
       <c r="D149" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E149">
         <v>2</v>
@@ -5647,16 +5648,16 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B150" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C150" t="s">
         <v>196</v>
       </c>
       <c r="D150" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E150">
         <v>2</v>
@@ -5664,16 +5665,16 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B151" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C151" t="s">
         <v>196</v>
       </c>
       <c r="D151" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -5681,16 +5682,16 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B152" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C152" t="s">
         <v>196</v>
       </c>
       <c r="D152" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E152">
         <v>3</v>
@@ -5698,16 +5699,16 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B153" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C153" t="s">
         <v>196</v>
       </c>
       <c r="D153" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E153">
         <v>3</v>
@@ -5715,16 +5716,16 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B154" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C154" t="s">
         <v>196</v>
       </c>
       <c r="D154" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E154">
         <v>3</v>
@@ -5732,16 +5733,16 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B155" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C155" t="s">
         <v>196</v>
       </c>
       <c r="D155" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E155">
         <v>3</v>
@@ -5749,16 +5750,16 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B156" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C156" t="s">
         <v>196</v>
       </c>
       <c r="D156" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E156">
         <v>3</v>
@@ -5766,16 +5767,16 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
+        <v>219</v>
+      </c>
+      <c r="B157" t="s">
         <v>220</v>
       </c>
-      <c r="B157" t="s">
-        <v>221</v>
-      </c>
       <c r="C157" t="s">
         <v>196</v>
       </c>
       <c r="D157" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E157">
         <v>3</v>
@@ -5783,16 +5784,16 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B158" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C158" t="s">
         <v>196</v>
       </c>
       <c r="D158" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E158">
         <v>3</v>
@@ -5800,16 +5801,16 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B159" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C159" t="s">
         <v>196</v>
       </c>
       <c r="D159" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E159">
         <v>2</v>
@@ -5817,16 +5818,16 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B160" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C160" t="s">
         <v>196</v>
       </c>
       <c r="D160" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E160">
         <v>3</v>
@@ -5834,16 +5835,16 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B161" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C161" t="s">
         <v>196</v>
       </c>
       <c r="D161" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E161">
         <v>3</v>
@@ -5851,16 +5852,16 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B162" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C162" t="s">
         <v>196</v>
       </c>
       <c r="D162" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E162">
         <v>3</v>
@@ -5868,16 +5869,16 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B163" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C163" t="s">
         <v>196</v>
       </c>
       <c r="D163" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E163">
         <v>3</v>
@@ -5885,16 +5886,16 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B164" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C164" t="s">
         <v>196</v>
       </c>
       <c r="D164" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E164">
         <v>3</v>
@@ -5902,16 +5903,16 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
+        <v>210</v>
+      </c>
+      <c r="B165" t="s">
         <v>211</v>
       </c>
-      <c r="B165" t="s">
-        <v>212</v>
-      </c>
       <c r="C165" t="s">
         <v>196</v>
       </c>
       <c r="D165" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E165">
         <v>2</v>
@@ -5919,16 +5920,16 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B166" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C166" t="s">
         <v>196</v>
       </c>
       <c r="D166" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E166">
         <v>3</v>
@@ -5939,13 +5940,13 @@
         <v>192</v>
       </c>
       <c r="B167" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C167" t="s">
         <v>196</v>
       </c>
       <c r="D167" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E167">
         <v>2</v>
@@ -5956,13 +5957,13 @@
         <v>192</v>
       </c>
       <c r="B168" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C168" t="s">
         <v>196</v>
       </c>
       <c r="D168" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E168">
         <v>2</v>
@@ -5973,13 +5974,13 @@
         <v>192</v>
       </c>
       <c r="B169" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C169" t="s">
         <v>196</v>
       </c>
       <c r="D169" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E169">
         <v>2</v>
@@ -5990,13 +5991,13 @@
         <v>192</v>
       </c>
       <c r="B170" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C170" t="s">
         <v>196</v>
       </c>
       <c r="D170" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E170">
         <v>2</v>
@@ -6007,13 +6008,13 @@
         <v>192</v>
       </c>
       <c r="B171" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C171" t="s">
         <v>196</v>
       </c>
       <c r="D171" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E171">
         <v>2</v>
@@ -6024,13 +6025,13 @@
         <v>192</v>
       </c>
       <c r="B172" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C172" t="s">
         <v>196</v>
       </c>
       <c r="D172" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E172">
         <v>2</v>
@@ -6041,13 +6042,13 @@
         <v>192</v>
       </c>
       <c r="B173" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C173" t="s">
         <v>196</v>
       </c>
       <c r="D173" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E173">
         <v>2</v>
@@ -6058,13 +6059,13 @@
         <v>192</v>
       </c>
       <c r="B174" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C174" t="s">
         <v>196</v>
       </c>
       <c r="D174" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E174">
         <v>2</v>
@@ -6075,13 +6076,13 @@
         <v>192</v>
       </c>
       <c r="B175" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C175" t="s">
         <v>196</v>
       </c>
       <c r="D175" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E175">
         <v>3</v>
@@ -6092,13 +6093,13 @@
         <v>192</v>
       </c>
       <c r="B176" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C176" t="s">
         <v>196</v>
       </c>
       <c r="D176" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E176">
         <v>3</v>
@@ -6109,13 +6110,13 @@
         <v>192</v>
       </c>
       <c r="B177" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C177" t="s">
         <v>196</v>
       </c>
       <c r="D177" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E177">
         <v>3</v>
@@ -6126,13 +6127,13 @@
         <v>192</v>
       </c>
       <c r="B178" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C178" t="s">
         <v>196</v>
       </c>
       <c r="D178" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E178">
         <v>2</v>
@@ -6143,13 +6144,13 @@
         <v>192</v>
       </c>
       <c r="B179" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C179" t="s">
         <v>196</v>
       </c>
       <c r="D179" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E179">
         <v>3</v>
@@ -6157,16 +6158,16 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B180" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C180" t="s">
         <v>196</v>
       </c>
       <c r="D180" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E180">
         <v>3</v>
@@ -6174,16 +6175,16 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B181" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C181" t="s">
         <v>196</v>
       </c>
       <c r="D181" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E181">
         <v>3</v>
@@ -6191,16 +6192,16 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B182" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C182" t="s">
         <v>196</v>
       </c>
       <c r="D182" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E182">
         <v>3</v>
@@ -6208,16 +6209,16 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
+        <v>408</v>
+      </c>
+      <c r="B183" t="s">
         <v>198</v>
       </c>
-      <c r="B183" t="s">
-        <v>199</v>
-      </c>
       <c r="C183" t="s">
         <v>196</v>
       </c>
       <c r="D183" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E183">
         <v>3</v>
@@ -6225,7 +6226,7 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
-        <v>198</v>
+        <v>408</v>
       </c>
       <c r="B184" t="s">
         <v>197</v>
@@ -6234,7 +6235,7 @@
         <v>196</v>
       </c>
       <c r="D184" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E184">
         <v>3</v>
